--- a/0_Document/스테이지.xlsx
+++ b/0_Document/스테이지.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Project LinkDeploy\0_Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F30505-A6CB-4A6C-8383-CAD53F3D5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5AA50A-7990-48D5-9837-457F14DA7365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,6 +424,9 @@
       <c r="E2">
         <v>3</v>
       </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -441,6 +444,9 @@
       <c r="E3">
         <v>5</v>
       </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -458,6 +464,9 @@
       <c r="E4">
         <v>7</v>
       </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -475,6 +484,9 @@
       <c r="E5">
         <v>7</v>
       </c>
+      <c r="F5">
+        <v>700</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -491,6 +503,9 @@
       </c>
       <c r="E6">
         <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -508,6 +523,9 @@
       </c>
       <c r="E7">
         <v>9</v>
+      </c>
+      <c r="F7">
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
